--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487581_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487581_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.26</v>
+        <v>12.533</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1834</v>
+        <v>7.4837</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0766</v>
+        <v>5.0493</v>
       </c>
       <c r="G2" t="n">
         <v>9.963200000000001</v>
@@ -610,13 +610,13 @@
         <v>3.2985</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6137</v>
+        <v>-0.3407</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3634</v>
+        <v>-0.0631</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2503</v>
+        <v>-0.2776</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8092</v>
+        <v>6.6734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1379</v>
+        <v>3.8386</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6713</v>
+        <v>2.8348</v>
       </c>
       <c r="G3" t="n">
         <v>4.9109</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4495</v>
+        <v>0.4147</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2905</v>
+        <v>0.4102</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.159</v>
+        <v>0.0045</v>
       </c>
       <c r="V3" t="n">
         <v>0.3776</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7802</v>
+        <v>6.3051</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7042</v>
+        <v>4.3653</v>
       </c>
       <c r="F4" t="n">
-        <v>2.076</v>
+        <v>1.9397</v>
       </c>
       <c r="G4" t="n">
         <v>3.3558</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5159</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6662</v>
+        <v>-0.0051</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1503</v>
+        <v>0.014</v>
       </c>
       <c r="V4" t="n">
         <v>0.6119</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.6598</v>
+        <v>5.196</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9115</v>
+        <v>1.6112</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7482</v>
+        <v>3.5847</v>
       </c>
       <c r="G5" t="n">
         <v>4.7268</v>
@@ -844,13 +844,13 @@
         <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0592</v>
+        <v>-0.1043</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5083</v>
+        <v>4.2418</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3487</v>
+        <v>0.4093</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1596</v>
+        <v>3.8325</v>
       </c>
       <c r="G6" t="n">
         <v>0.2257</v>
@@ -922,13 +922,13 @@
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4183</v>
+        <v>1.1519</v>
       </c>
       <c r="T6" t="n">
-        <v>0.923</v>
+        <v>0.9836</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4953</v>
+        <v>0.1683</v>
       </c>
       <c r="V6" t="n">
         <v>1.506</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3832</v>
+        <v>3.302</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0297</v>
+        <v>1.893</v>
       </c>
       <c r="F7" t="n">
-        <v>3.413</v>
+        <v>1.409</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2506</v>
+        <v>2.0381</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3075</v>
+        <v>1.5621</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5581</v>
+        <v>0.476</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6581</v>
+        <v>1.7619</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3717</v>
+        <v>1.6807</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0298</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5925</v>
+        <v>0.2762</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.1187</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5283</v>
+        <v>0.3948</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1045</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6734</v>
+        <v>0.8162</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0595</v>
+        <v>0.8476</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6139</v>
+        <v>-0.0314</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8358</v>
+        <v>1.2239</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3604</v>
+        <v>3.2648</v>
       </c>
       <c r="E8" t="n">
-        <v>2.333</v>
+        <v>-0.2299</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0274</v>
+        <v>3.4947</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0381</v>
+        <v>1.2506</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5621</v>
+        <v>-1.3075</v>
       </c>
       <c r="I8" t="n">
-        <v>0.476</v>
+        <v>2.5581</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7619</v>
+        <v>0.6581</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6807</v>
+        <v>-1.3717</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.0298</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2762</v>
+        <v>0.5925</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1187</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3948</v>
+        <v>0.5283</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>3.1045</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8746</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2875</v>
+        <v>-0.2597</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.413</v>
+        <v>-0.5322</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2239</v>
+        <v>1.8358</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7522</v>
+        <v>2.7795</v>
       </c>
       <c r="E9" t="n">
         <v>2.2364</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5158</v>
+        <v>0.5431</v>
       </c>
       <c r="G9" t="n">
         <v>2.85</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3217</v>
+        <v>-0.2944</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3217</v>
+        <v>-0.2944</v>
       </c>
       <c r="V9" t="n">
         <v>0.6119</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.525</v>
+        <v>0.1574</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4524</v>
+        <v>-3.493</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9775</v>
+        <v>3.6504</v>
       </c>
       <c r="G10" t="n">
         <v>0.2079</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>2.753</v>
+        <v>1.3854</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2577</v>
+        <v>1.2172</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4953</v>
+        <v>0.1683</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5538</v>
+        <v>-0.2207</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9448</v>
+        <v>-1.8842</v>
       </c>
       <c r="F11" t="n">
-        <v>1.391</v>
+        <v>1.6636</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1246</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3768</v>
+        <v>0.7099</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5596</v>
+        <v>0.6202</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1828</v>
+        <v>0.0897</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8293</v>
+        <v>-0.5474</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5856</v>
+        <v>-1.3854</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7562</v>
+        <v>0.838</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1233</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7822</v>
+        <v>-0.5002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4794</v>
+        <v>-0.3976</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0971</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8215</v>
+        <v>-2.5212</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7243</v>
+        <v>1.6971</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7997</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4915</v>
+        <v>-0.2184</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0536</v>
+        <v>0.0264</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>42.5581</v>
+        <v>42.8608</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0211</v>
+        <v>12.3238</v>
       </c>
       <c r="F14" t="n">
         <v>30.5369</v>
@@ -1546,13 +1546,13 @@
         <v>22.3137</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1197</v>
+        <v>2.422600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2859</v>
+        <v>3.5888</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1664</v>
+        <v>-1.1663</v>
       </c>
       <c r="V14" t="n">
         <v>5.2253</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5674</v>
+        <v>1.1463</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9304</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4978</v>
+        <v>1.8766</v>
       </c>
       <c r="G15" t="n">
         <v>0.9083</v>
@@ -1624,13 +1624,13 @@
         <v>0.9702</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0007</v>
+        <v>-0.4217</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6373</v>
+        <v>-0.2585</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1567</v>
+        <v>-0.0725</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0595</v>
+        <v>-0.6591</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2162</v>
+        <v>0.5865</v>
       </c>
       <c r="G16" t="n">
         <v>-1.6129</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1683</v>
+        <v>0.2321</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0155</v>
+        <v>0.3859</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0478</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.062</v>
+        <v>-0.9992</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7201</v>
+        <v>0.2025</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6581</v>
+        <v>-1.2017</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6199</v>
+        <v>-0.2214</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.7995</v>
+        <v>0.828</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1796</v>
+        <v>-1.0494</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.2068</v>
+        <v>0.8769</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.4633</v>
+        <v>2.1709</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7435</v>
+        <v>-1.2941</v>
       </c>
       <c r="M17" t="n">
-        <v>0.587</v>
+        <v>-1.0983</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3362</v>
+        <v>-1.3429</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9231</v>
+        <v>0.2447</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1996</v>
+        <v>-0.5061</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4867</v>
+        <v>-0.0743</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2871</v>
+        <v>-0.4318</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8634</v>
+        <v>-1.3985</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4982</v>
+        <v>-2.9203</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3652</v>
+        <v>1.5218</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2214</v>
+        <v>-2.6199</v>
       </c>
       <c r="H18" t="n">
-        <v>0.828</v>
+        <v>-2.7995</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0494</v>
+        <v>0.1796</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8769</v>
+        <v>-3.2068</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1709</v>
+        <v>-2.4633</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2941</v>
+        <v>-0.7435</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0983</v>
+        <v>0.587</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3429</v>
+        <v>-0.3362</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2447</v>
+        <v>0.9231</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3703</v>
+        <v>-0.1368</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.775</v>
+        <v>0.2865</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.4234</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7539</v>
+        <v>-3.5034</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8681</v>
+        <v>-0.8339</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8859</v>
+        <v>-2.6695</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6177</v>
+        <v>-1.4645</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5332</v>
+        <v>-1.3198</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0844</v>
+        <v>-0.1446</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.899</v>
+        <v>0.3625</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2317</v>
+        <v>0.3625</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7187</v>
+        <v>-1.827</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3015</v>
+        <v>-1.6824</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4171</v>
+        <v>-0.1446</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-0.194</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4363</v>
+        <v>-0.6211</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0011</v>
+        <v>-0.2263</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4374</v>
+        <v>-0.3948</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7833</v>
+        <v>-3.9541</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8458</v>
+        <v>-3.0683</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9376</v>
+        <v>-0.8859</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3579</v>
+        <v>-2.6177</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2189</v>
+        <v>-1.5332</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.139</v>
+        <v>-1.0844</v>
       </c>
       <c r="J20" t="n">
         <v>-1.899</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.899</v>
+        <v>-1.2317</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4589</v>
+        <v>-0.7187</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3198</v>
+        <v>-0.3015</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.139</v>
+        <v>-0.4171</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6507</v>
+        <v>-0.6365</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7115</v>
+        <v>-0.1991</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0608</v>
+        <v>-0.4374</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3299</v>
+        <v>-0.894</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3009</v>
+        <v>-4.7689</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3344</v>
+        <v>-2.8943</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9665</v>
+        <v>-1.8746</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4645</v>
+        <v>-0.7896</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3198</v>
+        <v>-1.1444</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1446</v>
+        <v>0.3548</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3625</v>
+        <v>1.115</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3625</v>
+        <v>0.4655</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.6495</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.827</v>
+        <v>-1.9046</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6824</v>
+        <v>-1.6099</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1446</v>
+        <v>-0.2948</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.194</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-4.0747</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4186</v>
+        <v>-0.233</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7268</v>
+        <v>0.0653</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6918</v>
+        <v>-0.2983</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0325</v>
+        <v>-4.7754</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9944</v>
+        <v>-2.9468</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0381</v>
+        <v>-1.8286</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7896</v>
+        <v>-3.3579</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1444</v>
+        <v>-3.2189</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3548</v>
+        <v>-0.139</v>
       </c>
       <c r="J22" t="n">
-        <v>1.115</v>
+        <v>-1.899</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4655</v>
+        <v>-1.899</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6495</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9046</v>
+        <v>-1.4589</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6099</v>
+        <v>-1.3198</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2948</v>
+        <v>-0.139</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5224</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0747</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4966</v>
+        <v>0.6586</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0348</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4618</v>
+        <v>0.0482</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>-0.3299</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1364</v>
+        <v>-7.0531</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5332</v>
+        <v>-4.0772</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6032</v>
+        <v>-2.9758</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.3914</v>
+        <v>-2.1182</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.0289</v>
+        <v>-0.7613</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3625</v>
+        <v>-1.3569</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5457</v>
+        <v>-0.0247</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.5457</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.8457</v>
+        <v>-2.0935</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4832</v>
+        <v>-1.4039</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3625</v>
+        <v>-0.6896</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7761</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1344</v>
+        <v>-3.8806</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0312</v>
+        <v>-0.5184</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1469</v>
+        <v>-0.1719</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1157</v>
+        <v>-0.3465</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4079</v>
+        <v>-7.1303</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3775</v>
+        <v>-4.6333</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0304</v>
+        <v>-2.497</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1182</v>
+        <v>-6.3914</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7613</v>
+        <v>-5.0289</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3569</v>
+        <v>-1.3625</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0247</v>
+        <v>-2.5457</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6425999999999999</v>
+        <v>-2.5457</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0935</v>
+        <v>-3.8457</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4039</v>
+        <v>-2.4832</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6896</v>
+        <v>-1.3625</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9105</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8806</v>
+        <v>-2.1344</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8733</v>
+        <v>0.0373</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4722</v>
+        <v>0.0468</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4011</v>
+        <v>-0.0095</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.941700000000001</v>
+        <v>-9.381600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3753</v>
+        <v>-7.9759</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5664</v>
+        <v>-1.4057</v>
       </c>
       <c r="G25" t="n">
         <v>-6.1963</v>
@@ -2404,13 +2404,13 @@
         <v>1.5523</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7472</v>
+        <v>0.3073</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3604</v>
+        <v>0.7598</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6133</v>
+        <v>-0.4525</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-42.5579</v>
+        <v>-41.8907</v>
       </c>
       <c r="E26" t="n">
         <v>-30.5369</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.0212</v>
+        <v>-11.3539</v>
       </c>
       <c r="G26" t="n">
         <v>-26.4815</v>
@@ -2482,13 +2482,13 @@
         <v>13.5824</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1198</v>
+        <v>-1.4524</v>
       </c>
       <c r="T26" t="n">
         <v>1.1661</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.286099999999999</v>
+        <v>-2.6186</v>
       </c>
       <c r="V26" t="n">
         <v>-5.2255</v>
